--- a/tracking_forms/039_daily_portion_tracker_form--tracking_forms.xlsx
+++ b/tracking_forms/039_daily_portion_tracker_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,36 +525,40 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Page</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What was the first thing you had for breakfast?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select your first breakfast item.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>first_page_header</t>
+          <t>first_page_servings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Which of the following items did you eat</t>
+          <t>How many servings?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,41 +570,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>breakfast_item</t>
+          <t>did_you_eat_snacks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Breakfast Item</t>
+          <t>Did you eat any snacks?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>breakfast_servings</t>
+          <t>snacks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How many servings</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What snacks did you have?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +620,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_page_separator</t>
+          <t>first_page_servings_snacks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>_______________________________________</t>
+          <t>How many servings of snacks?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,18 +643,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lunch_item</t>
+          <t>second_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lunch Item</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What was the main course for lunch?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select your main course item.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,64 +670,68 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lunch_servings</t>
+          <t>second_page_servings</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How many servings</t>
+          <t>Second Page Servings</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>first_page_separator</t>
+          <t>did_you_eat_snacks_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>_______________________________________</t>
+          <t>Did you eat any additional snacks?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dinner_item</t>
+          <t>additional_snacks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dinner Item</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Additional Snacks</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,12 +743,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dinner_servings</t>
+          <t>second_page_servings_snacks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How many servings</t>
+          <t>How many servings of additional snacks?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,92 +761,100 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>first_page_separator</t>
+          <t>third_page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>_______________________________________</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What was the main course for dinner?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please select your main course item.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>snacks</t>
+          <t>third_page_servings</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Snacks</t>
+          <t>Third Page Servings</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>snacks_servings</t>
+          <t>did_you_eat_snacks_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How many servings</t>
+          <t>Did You Eat Snacks 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>first_page_footer</t>
+          <t>additional_snacks_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Please let us know if you have any questions</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Additional Snacks 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,16 +866,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>first_page_footer</t>
+          <t>third_page_servings_snacks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>_______________________________________</t>
+          <t>Third Page Servings Snacks</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fourth_page</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Additional comments or questions</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,10 +915,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
@@ -896,109 +943,109 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>first_page_header_choices</t>
+          <t>first_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>apples</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Apples</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>first_page_header_choices</t>
+          <t>first_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bananas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bananas</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>breakfast_item_choices</t>
+          <t>first_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>apples</t>
+          <t>carrots</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apples</t>
+          <t>Carrots</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>breakfast_item_choices</t>
+          <t>first_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>carrots</t>
+          <t>oranges</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Carrots</t>
+          <t>Oranges</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>breakfast_item_choices</t>
+          <t>did_you_eat_snacks_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>oranges</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oranges</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>breakfast_item_choices</t>
+          <t>did_you_eat_snacks_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bananas</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>breakfast_item_choices</t>
+          <t>snacks_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1015,58 +1062,58 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>breakfast_item_choices</t>
+          <t>snacks_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>carrots</t>
+          <t>bananas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Carrots</t>
+          <t>Bananas</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>breakfast_item_choices</t>
+          <t>snacks_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>oranges</t>
+          <t>carrots</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oranges</t>
+          <t>Carrots</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>breakfast_item_choices</t>
+          <t>snacks_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bananas</t>
+          <t>oranges</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Oranges</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lunch_item_choices</t>
+          <t>second_page_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1083,109 +1130,109 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lunch_item_choices</t>
+          <t>second_page_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>carrots</t>
+          <t>bananas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Carrots</t>
+          <t>Bananas</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lunch_item_choices</t>
+          <t>second_page_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>oranges</t>
+          <t>carrots</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oranges</t>
+          <t>Carrots</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lunch_item_choices</t>
+          <t>second_page_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bananas</t>
+          <t>oranges</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Oranges</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>lunch_item_choices</t>
+          <t>did_you_eat_snacks_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>apples</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Apples</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lunch_item_choices</t>
+          <t>did_you_eat_snacks_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>carrots</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carrots</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lunch_item_choices</t>
+          <t>additional_snacks_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>oranges</t>
+          <t>apples</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oranges</t>
+          <t>Apples</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>lunch_item_choices</t>
+          <t>additional_snacks_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1202,58 +1249,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>dinner_item_choices</t>
+          <t>additional_snacks_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>apples</t>
+          <t>carrots</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Apples</t>
+          <t>Carrots</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dinner_item_choices</t>
+          <t>additional_snacks_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carrots</t>
+          <t>oranges</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carrots</t>
+          <t>Oranges</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dinner_item_choices</t>
+          <t>third_page_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>oranges</t>
+          <t>apples</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oranges</t>
+          <t>Apples</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dinner_item_choices</t>
+          <t>third_page_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1270,75 +1317,75 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dinner_item_choices</t>
+          <t>third_page_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>apples</t>
+          <t>carrots</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Apples</t>
+          <t>Carrots</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dinner_item_choices</t>
+          <t>third_page_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>carrots</t>
+          <t>oranges</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Carrots</t>
+          <t>Oranges</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dinner_item_choices</t>
+          <t>did_you_eat_snacks_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>oranges</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oranges</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dinner_item_choices</t>
+          <t>did_you_eat_snacks_3_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bananas</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>snacks_choices</t>
+          <t>additional_snacks_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1355,119 +1402,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>snacks_choices</t>
+          <t>additional_snacks_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>carrots</t>
+          <t>bananas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carrots</t>
+          <t>Bananas</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>snacks_choices</t>
+          <t>additional_snacks_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>oranges</t>
+          <t>carrots</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oranges</t>
+          <t>Carrots</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>snacks_choices</t>
+          <t>additional_snacks_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>bananas</t>
+          <t>oranges</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bananas</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>snacks_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>apples</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Apples</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>snacks_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>carrots</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Carrots</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>snacks_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>oranges</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
           <t>Oranges</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>snacks_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>bananas</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Bananas</t>
         </is>
       </c>
     </row>
